--- a/Data/cosp_WBID.xlsx
+++ b/Data/cosp_WBID.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pinellasgov.sharepoint.com/sites/BCC-PW-ENVMT/Monitoring and Assessment/R/water_quality_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{87882669-4CEB-4158-9B6F-F8BA491F35BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CE841B8-AE86-4BBE-9A77-BFB0DD91F370}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="13_ncr:1_{87882669-4CEB-4158-9B6F-F8BA491F35BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BF060E4-F34D-4C4D-9937-9975BB7CA158}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="-24630" yWindow="1470" windowWidth="21600" windowHeight="11295" xr2:uid="{09EBD490-D41C-4997-8235-31EADA5BD482}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{09EBD490-D41C-4997-8235-31EADA5BD482}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="88">
   <si>
     <t>SampleName</t>
   </si>
@@ -281,30 +281,6 @@
     <t>DIRECT RUNOFF TO BAY (YACHT BASIN - BASIN A)</t>
   </si>
   <si>
-    <t>E6-A</t>
-  </si>
-  <si>
-    <t>E6-B</t>
-  </si>
-  <si>
-    <t>E6-C</t>
-  </si>
-  <si>
-    <t>E6-D</t>
-  </si>
-  <si>
-    <t>E7-A</t>
-  </si>
-  <si>
-    <t>E7-B</t>
-  </si>
-  <si>
-    <t>E7-C</t>
-  </si>
-  <si>
-    <t>E7-D</t>
-  </si>
-  <si>
     <t>1558C</t>
   </si>
   <si>
@@ -315,6 +291,15 @@
   </si>
   <si>
     <t>1558B</t>
+  </si>
+  <si>
+    <t>E6</t>
+  </si>
+  <si>
+    <t>E7</t>
+  </si>
+  <si>
+    <t>DISP_TYPE</t>
   </si>
 </sst>
 </file>
@@ -674,7 +659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D012203-851B-4963-A9B8-126EC2AC6A7B}">
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.85546875" bestFit="1" customWidth="1"/>
@@ -690,7 +675,7 @@
     <col min="11" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -724,8 +709,11 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -759,8 +747,11 @@
       <c r="K2">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -794,8 +785,11 @@
       <c r="K3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -829,8 +823,11 @@
       <c r="K4" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -864,8 +861,11 @@
       <c r="K5">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -899,8 +899,11 @@
       <c r="K6" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -934,8 +937,11 @@
       <c r="K7" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -969,8 +975,11 @@
       <c r="K8" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -1004,8 +1013,11 @@
       <c r="K9" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -1039,8 +1051,11 @@
       <c r="K10" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>43</v>
       </c>
@@ -1074,8 +1089,11 @@
       <c r="K11" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -1109,8 +1127,11 @@
       <c r="K12" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>47</v>
       </c>
@@ -1144,8 +1165,11 @@
       <c r="K13" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>50</v>
       </c>
@@ -1179,8 +1203,11 @@
       <c r="K14" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>53</v>
       </c>
@@ -1214,8 +1241,11 @@
       <c r="K15" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>54</v>
       </c>
@@ -1249,8 +1279,11 @@
       <c r="K16" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>55</v>
       </c>
@@ -1284,8 +1317,11 @@
       <c r="K17" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L17" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>59</v>
       </c>
@@ -1319,8 +1355,11 @@
       <c r="K18" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L18" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>60</v>
       </c>
@@ -1354,8 +1393,11 @@
       <c r="K19" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>63</v>
       </c>
@@ -1389,8 +1431,11 @@
       <c r="K20" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>64</v>
       </c>
@@ -1424,8 +1469,11 @@
       <c r="K21" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L21" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>65</v>
       </c>
@@ -1459,8 +1507,11 @@
       <c r="K22" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>68</v>
       </c>
@@ -1494,8 +1545,11 @@
       <c r="K23" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L23" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>71</v>
       </c>
@@ -1529,8 +1583,11 @@
       <c r="K24" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>72</v>
       </c>
@@ -1564,8 +1621,11 @@
       <c r="K25" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L25" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>75</v>
       </c>
@@ -1599,8 +1659,11 @@
       <c r="K26" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L26" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>76</v>
       </c>
@@ -1634,117 +1697,42 @@
       <c r="K27">
         <v>2</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L27" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>85</v>
+      </c>
+      <c r="E28" t="s">
         <v>81</v>
       </c>
-      <c r="E28" t="s">
-        <v>89</v>
-      </c>
       <c r="I28" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="J28" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+      <c r="L28" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E29" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="I29" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J29" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
         <v>83</v>
       </c>
-      <c r="E30" t="s">
-        <v>89</v>
-      </c>
-      <c r="I30" t="s">
-        <v>90</v>
-      </c>
-      <c r="J30" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>84</v>
-      </c>
-      <c r="E31" t="s">
-        <v>89</v>
-      </c>
-      <c r="I31" t="s">
-        <v>90</v>
-      </c>
-      <c r="J31" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>85</v>
-      </c>
-      <c r="E32" t="s">
-        <v>92</v>
-      </c>
-      <c r="I32" t="s">
-        <v>78</v>
-      </c>
-      <c r="J32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>86</v>
-      </c>
-      <c r="E33" t="s">
-        <v>92</v>
-      </c>
-      <c r="I33" t="s">
-        <v>78</v>
-      </c>
-      <c r="J33" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>87</v>
-      </c>
-      <c r="E34" t="s">
-        <v>92</v>
-      </c>
-      <c r="I34" t="s">
-        <v>78</v>
-      </c>
-      <c r="J34" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>88</v>
-      </c>
-      <c r="E35" t="s">
-        <v>92</v>
-      </c>
-      <c r="I35" t="s">
-        <v>78</v>
-      </c>
-      <c r="J35" t="s">
-        <v>91</v>
+      <c r="L29" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1753,6 +1741,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ebcefb84-3943-4c67-86e4-95e0d5522177" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20a86c8e-58bd-487e-986c-19c6170a5cfd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B730D8DC4DFB374C886B31D158660B04" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e156938d0b65e910bf65aa8aa145b3eb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20a86c8e-58bd-487e-986c-19c6170a5cfd" xmlns:ns3="ebcefb84-3943-4c67-86e4-95e0d5522177" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="258c2e9f717cb07b6517e945f6b981b4" ns2:_="" ns3:_="">
     <xsd:import namespace="20a86c8e-58bd-487e-986c-19c6170a5cfd"/>
@@ -1965,27 +1973,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ebcefb84-3943-4c67-86e4-95e0d5522177" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20a86c8e-58bd-487e-986c-19c6170a5cfd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D709A9B-4334-4A9B-808C-6F6ABEA25371}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ebcefb84-3943-4c67-86e4-95e0d5522177"/>
+    <ds:schemaRef ds:uri="20a86c8e-58bd-487e-986c-19c6170a5cfd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25637DD9-C791-4F90-B600-E2CD8294252D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13C97529-E099-4195-B0C3-37CA4BF46A9F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2002,23 +2009,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D709A9B-4334-4A9B-808C-6F6ABEA25371}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ebcefb84-3943-4c67-86e4-95e0d5522177"/>
-    <ds:schemaRef ds:uri="20a86c8e-58bd-487e-986c-19c6170a5cfd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25637DD9-C791-4F90-B600-E2CD8294252D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>